--- a/nriss-patch-1/ig/StructureDefinition-fr-cda-evenement.xlsx
+++ b/nriss-patch-1/ig/StructureDefinition-fr-cda-evenement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T11:58:08+00:00</t>
+    <t>2026-06-01T14:28:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5251,7 +5251,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>168</v>
       </c>
@@ -5270,7 +5270,7 @@
         <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>74</v>
+        <v>162</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>74</v>
@@ -5556,7 +5556,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>177</v>
       </c>
@@ -5571,13 +5571,13 @@
         <v>62</v>
       </c>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>74</v>
+        <v>162</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>74</v>
@@ -5659,7 +5659,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>180</v>
       </c>
@@ -5674,13 +5674,13 @@
         <v>181</v>
       </c>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>74</v>
+        <v>162</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>74</v>
@@ -5968,7 +5968,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>192</v>
       </c>
@@ -5989,7 +5989,7 @@
         <v>75</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>74</v>
+        <v>162</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>74</v>

--- a/nriss-patch-1/ig/StructureDefinition-fr-cda-evenement.xlsx
+++ b/nriss-patch-1/ig/StructureDefinition-fr-cda-evenement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:28:18+00:00</t>
+    <t>2026-06-01T15:28:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
